--- a/business_registration_forms/025_remote_housing_provider_registration--business_registration_forms.xlsx
+++ b/business_registration_forms/025_remote_housing_provider_registration--business_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'agency'}</t>
+          <t>agency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Agency'}</t>
+          <t>Agency</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'housing_coordinator'}</t>
+          <t>housing_coordinator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Housing Coordinator'}</t>
+          <t>Housing Coordinator</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'i_confirm_that_i_have_read_and_agree_to_the_terms_and_conditions.'}</t>
+          <t>i_confirm_that_i_have_read_and_agree_to_the_terms_and_conditions.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'I confirm that I have read and agree to the terms and conditions.'}</t>
+          <t>I confirm that I have read and agree to the terms and conditions.</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_none}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': None}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'i_am_aware_that_i_must_provide_accurate_and_truthful_information_for_all_fields.'}</t>
+          <t>i_am_aware_that_i_must_provide_accurate_and_truthful_information_for_all_fields.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'I am aware that I must provide accurate and truthful information for all fields.'}</t>
+          <t>I am aware that I must provide accurate and truthful information for all fields.</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'i_am_aware_that_i_must_provide_accurate_and_truthful_information_for_all_fields.'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'I am aware that I must provide accurate and truthful information for all fields.'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
